--- a/data/nzd0066/nzd0066.xlsx
+++ b/data/nzd0066/nzd0066.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P310"/>
+  <dimension ref="A1:P312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17144,6 +17144,114 @@
         <v>397.15</v>
       </c>
       <c r="P310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>441.69</v>
+      </c>
+      <c r="C311" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="D311" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="E311" t="n">
+        <v>375.33</v>
+      </c>
+      <c r="F311" t="n">
+        <v>394.8</v>
+      </c>
+      <c r="G311" t="n">
+        <v>396.64</v>
+      </c>
+      <c r="H311" t="n">
+        <v>399.85</v>
+      </c>
+      <c r="I311" t="n">
+        <v>402.68</v>
+      </c>
+      <c r="J311" t="n">
+        <v>408.55</v>
+      </c>
+      <c r="K311" t="n">
+        <v>400.83</v>
+      </c>
+      <c r="L311" t="n">
+        <v>400.44</v>
+      </c>
+      <c r="M311" t="n">
+        <v>397</v>
+      </c>
+      <c r="N311" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="O311" t="n">
+        <v>399.19</v>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>421.34</v>
+      </c>
+      <c r="C312" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="D312" t="n">
+        <v>366.2</v>
+      </c>
+      <c r="E312" t="n">
+        <v>376.08</v>
+      </c>
+      <c r="F312" t="n">
+        <v>396.25</v>
+      </c>
+      <c r="G312" t="n">
+        <v>397.48</v>
+      </c>
+      <c r="H312" t="n">
+        <v>400.52</v>
+      </c>
+      <c r="I312" t="n">
+        <v>403.6</v>
+      </c>
+      <c r="J312" t="n">
+        <v>410</v>
+      </c>
+      <c r="K312" t="n">
+        <v>402.61</v>
+      </c>
+      <c r="L312" t="n">
+        <v>401.31</v>
+      </c>
+      <c r="M312" t="n">
+        <v>398.35</v>
+      </c>
+      <c r="N312" t="n">
+        <v>403.51</v>
+      </c>
+      <c r="O312" t="n">
+        <v>400.16</v>
+      </c>
+      <c r="P312" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17160,7 +17268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B313"/>
+  <dimension ref="A1:B315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20293,6 +20401,26 @@
       </c>
       <c r="B313" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -20461,28 +20589,28 @@
         <v>0.0103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1036830328548805</v>
+        <v>0.1002476772432569</v>
       </c>
       <c r="J2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K2" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001845774866634509</v>
+        <v>0.0001752320084532633</v>
       </c>
       <c r="M2" t="n">
-        <v>40.0554977741487</v>
+        <v>39.83947557911845</v>
       </c>
       <c r="N2" t="n">
-        <v>2777.661383937539</v>
+        <v>2758.996880796678</v>
       </c>
       <c r="O2" t="n">
-        <v>52.70352344898336</v>
+        <v>52.52615425477747</v>
       </c>
       <c r="P2" t="n">
-        <v>431.0034985793014</v>
+        <v>431.0446249336604</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20543,28 +20671,28 @@
         <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2020717634823941</v>
+        <v>-0.2059405842228673</v>
       </c>
       <c r="J3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1286618597404877</v>
+        <v>0.1341194926578154</v>
       </c>
       <c r="M3" t="n">
-        <v>3.018456686199517</v>
+        <v>3.014948624138558</v>
       </c>
       <c r="N3" t="n">
-        <v>14.81991799892339</v>
+        <v>14.79366288537522</v>
       </c>
       <c r="O3" t="n">
-        <v>3.849664660580632</v>
+        <v>3.84625309689511</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0794234222641</v>
+        <v>370.122060693208</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20625,28 +20753,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2646108134257596</v>
+        <v>0.2588224995421073</v>
       </c>
       <c r="J4" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K4" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2111109587696075</v>
+        <v>0.2046970778703325</v>
       </c>
       <c r="M4" t="n">
-        <v>2.883358829008453</v>
+        <v>2.892747707252046</v>
       </c>
       <c r="N4" t="n">
-        <v>14.02225815483302</v>
+        <v>14.06211888365364</v>
       </c>
       <c r="O4" t="n">
-        <v>3.744630576549977</v>
+        <v>3.749949184142852</v>
       </c>
       <c r="P4" t="n">
-        <v>362.4825496010701</v>
+        <v>362.5463486776935</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20707,28 +20835,28 @@
         <v>0.0935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1920267150173312</v>
+        <v>0.1916454170066131</v>
       </c>
       <c r="J5" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K5" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2290762523227162</v>
+        <v>0.2309153738339556</v>
       </c>
       <c r="M5" t="n">
-        <v>1.989098320356663</v>
+        <v>1.979009463119163</v>
       </c>
       <c r="N5" t="n">
-        <v>6.650469365377956</v>
+        <v>6.609124511977506</v>
       </c>
       <c r="O5" t="n">
-        <v>2.578850396083099</v>
+        <v>2.570821758111112</v>
       </c>
       <c r="P5" t="n">
-        <v>370.8291694684598</v>
+        <v>370.8333702040843</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20789,28 +20917,28 @@
         <v>0.0818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1047252959763318</v>
+        <v>0.1043393925174011</v>
       </c>
       <c r="J6" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K6" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06113132721796199</v>
+        <v>0.06152022406041868</v>
       </c>
       <c r="M6" t="n">
-        <v>2.050910500374187</v>
+        <v>2.042411234779506</v>
       </c>
       <c r="N6" t="n">
-        <v>9.026966982079129</v>
+        <v>8.97282904176828</v>
       </c>
       <c r="O6" t="n">
-        <v>3.004491135297145</v>
+        <v>2.995468083917483</v>
       </c>
       <c r="P6" t="n">
-        <v>392.9972741553815</v>
+        <v>393.0015234038981</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20871,28 +20999,28 @@
         <v>0.1274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09468308044184275</v>
+        <v>0.09489457664941743</v>
       </c>
       <c r="J7" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K7" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05587000307505807</v>
+        <v>0.05687424525652796</v>
       </c>
       <c r="M7" t="n">
-        <v>2.125570117862889</v>
+        <v>2.114544292218582</v>
       </c>
       <c r="N7" t="n">
-        <v>8.118868299481415</v>
+        <v>8.067937393700969</v>
       </c>
       <c r="O7" t="n">
-        <v>2.84936278832328</v>
+        <v>2.840411483165946</v>
       </c>
       <c r="P7" t="n">
-        <v>394.3492191345807</v>
+        <v>394.3468851040263</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -20953,28 +21081,28 @@
         <v>0.1062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3244576547065957</v>
+        <v>0.323409601969856</v>
       </c>
       <c r="J8" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K8" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2719042299325125</v>
+        <v>0.2734486055257762</v>
       </c>
       <c r="M8" t="n">
-        <v>2.505609742681638</v>
+        <v>2.495844501838541</v>
       </c>
       <c r="N8" t="n">
-        <v>15.10727834934646</v>
+        <v>15.01489236949229</v>
       </c>
       <c r="O8" t="n">
-        <v>3.886808247051359</v>
+        <v>3.87490546587814</v>
       </c>
       <c r="P8" t="n">
-        <v>392.2475340757238</v>
+        <v>392.2590848005063</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21035,28 +21163,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2404573462729928</v>
+        <v>0.2366939122913186</v>
       </c>
       <c r="J9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1612071030045904</v>
+        <v>0.1584801145038826</v>
       </c>
       <c r="M9" t="n">
-        <v>2.932805439901857</v>
+        <v>2.936801448297893</v>
       </c>
       <c r="N9" t="n">
-        <v>16.12294260743721</v>
+        <v>16.07272665909339</v>
       </c>
       <c r="O9" t="n">
-        <v>4.015338417548041</v>
+        <v>4.009080525393995</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5422605548968</v>
+        <v>399.5837426385914</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21117,28 +21245,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.155186643318459</v>
+        <v>0.1570123720305674</v>
       </c>
       <c r="J10" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K10" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08111700436694991</v>
+        <v>0.08390966217077245</v>
       </c>
       <c r="M10" t="n">
-        <v>2.88662645326254</v>
+        <v>2.875490350084157</v>
       </c>
       <c r="N10" t="n">
-        <v>14.6202442281251</v>
+        <v>14.54185652097421</v>
       </c>
       <c r="O10" t="n">
-        <v>3.823642795571404</v>
+        <v>3.813378622819168</v>
       </c>
       <c r="P10" t="n">
-        <v>403.6992805376453</v>
+        <v>403.6791505606101</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -21199,28 +21327,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01653157267826132</v>
+        <v>0.01597115276854776</v>
       </c>
       <c r="J11" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K11" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001092227663263334</v>
+        <v>0.001033972302606601</v>
       </c>
       <c r="M11" t="n">
-        <v>2.689343632952715</v>
+        <v>2.677892947181046</v>
       </c>
       <c r="N11" t="n">
-        <v>13.39486064151662</v>
+        <v>13.3149677109573</v>
       </c>
       <c r="O11" t="n">
-        <v>3.659898993348945</v>
+        <v>3.648968033699021</v>
       </c>
       <c r="P11" t="n">
-        <v>401.7070283563884</v>
+        <v>401.7132002650209</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -21281,28 +21409,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1157165235334523</v>
+        <v>-0.1126529454308731</v>
       </c>
       <c r="J12" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K12" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06056377416792658</v>
+        <v>0.05820059849735626</v>
       </c>
       <c r="M12" t="n">
-        <v>2.441904844053504</v>
+        <v>2.438773833842977</v>
       </c>
       <c r="N12" t="n">
-        <v>11.13121996011918</v>
+        <v>11.09537124414209</v>
       </c>
       <c r="O12" t="n">
-        <v>3.336348297183491</v>
+        <v>3.33097151656121</v>
       </c>
       <c r="P12" t="n">
-        <v>401.6471712650765</v>
+        <v>401.6133981207527</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -21363,28 +21491,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1969050893128351</v>
+        <v>-0.1931967202689224</v>
       </c>
       <c r="J13" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K13" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1768225724863752</v>
+        <v>0.1726400560190399</v>
       </c>
       <c r="M13" t="n">
-        <v>2.226625042341362</v>
+        <v>2.227393026672348</v>
       </c>
       <c r="N13" t="n">
-        <v>9.673135441731091</v>
+        <v>9.664473459876751</v>
       </c>
       <c r="O13" t="n">
-        <v>3.110166465276592</v>
+        <v>3.108773626347977</v>
       </c>
       <c r="P13" t="n">
-        <v>400.1417065261072</v>
+        <v>400.1008241665464</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -21445,28 +21573,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2423287711927529</v>
+        <v>-0.2326958052003788</v>
       </c>
       <c r="J14" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K14" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1824363033207558</v>
+        <v>0.1692830908255958</v>
       </c>
       <c r="M14" t="n">
-        <v>3.007896815358202</v>
+        <v>3.039137731978521</v>
       </c>
       <c r="N14" t="n">
-        <v>14.10320870816784</v>
+        <v>14.35629438858721</v>
       </c>
       <c r="O14" t="n">
-        <v>3.755423905255949</v>
+        <v>3.788970096027047</v>
       </c>
       <c r="P14" t="n">
-        <v>402.0664862928884</v>
+        <v>401.9602965130352</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -21527,28 +21655,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2367323770393096</v>
+        <v>-0.2306152251881365</v>
       </c>
       <c r="J15" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K15" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2643406688943634</v>
+        <v>0.2538976324422196</v>
       </c>
       <c r="M15" t="n">
-        <v>2.074434202971075</v>
+        <v>2.093507430458319</v>
       </c>
       <c r="N15" t="n">
-        <v>8.358449421043209</v>
+        <v>8.443869154263254</v>
       </c>
       <c r="O15" t="n">
-        <v>2.891098307052738</v>
+        <v>2.905833641876846</v>
       </c>
       <c r="P15" t="n">
-        <v>401.3748155735651</v>
+        <v>401.3073820282419</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -21590,7 +21718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P310"/>
+  <dimension ref="A1:P312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46913,6 +47041,170 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-35.272774256429564,174.0810121960133</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-35.27368509985813,174.0804033826581</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-35.27439372292355,174.08062708416793</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-35.275060244920425,174.08099749439418</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-35.275612428824516,174.08151602355073</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-35.276076028086266,174.08209930344017</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-35.27651313604226,174.08278110386428</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-35.2769112167824,174.08348874093517</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-35.27721349495382,174.0842463044154</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-35.27754639181197,174.08499834256077</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-35.27778775732391,174.08582364412572</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-35.278026862982024,174.08665329441138</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-35.27815033648408,174.0875205818183</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-35.278324192205915,174.08838607849492</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-35.27282663849006,174.08079777972014</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-35.27367854222695,174.08043470066102</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-35.27438911983591,174.0806487986444</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-35.27505789964193,174.08100522829142</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-35.275605126176,174.08152924633114</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-35.276070481397575,174.0821055916404</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-35.27650838936187,174.08278565993402</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-35.276904272723954,174.0834942732469</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-35.27720176980435,174.0842533549105</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-35.27753138343916,174.0850052730952</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-35.277780289517366,174.08582657039076</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-35.27801510325197,174.08665712260265</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-35.27813967637095,174.0875234089329</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-35.27831561407852,174.0883881547596</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0066/nzd0066.xlsx
+++ b/data/nzd0066/nzd0066.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P312"/>
+  <dimension ref="A1:P313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>421.34</v>
+        <v>441.69</v>
       </c>
       <c r="C312" t="n">
         <v>363.15</v>
@@ -17252,6 +17252,60 @@
         <v>400.16</v>
       </c>
       <c r="P312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>492.59</v>
+      </c>
+      <c r="C313" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="D313" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="E313" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="F313" t="n">
+        <v>396.05</v>
+      </c>
+      <c r="G313" t="n">
+        <v>397.26</v>
+      </c>
+      <c r="H313" t="n">
+        <v>400.07</v>
+      </c>
+      <c r="I313" t="n">
+        <v>403.48</v>
+      </c>
+      <c r="J313" t="n">
+        <v>409.68</v>
+      </c>
+      <c r="K313" t="n">
+        <v>403.42</v>
+      </c>
+      <c r="L313" t="n">
+        <v>401.18</v>
+      </c>
+      <c r="M313" t="n">
+        <v>398.24</v>
+      </c>
+      <c r="N313" t="n">
+        <v>403.74</v>
+      </c>
+      <c r="O313" t="n">
+        <v>399.62</v>
+      </c>
+      <c r="P313" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17268,7 +17322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B315"/>
+  <dimension ref="A1:B316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20421,6 +20475,16 @@
       </c>
       <c r="B315" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -20589,28 +20653,28 @@
         <v>0.0103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1002476772432569</v>
+        <v>0.1593667812860119</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001752320084532633</v>
+        <v>0.0004443533751359308</v>
       </c>
       <c r="M2" t="n">
-        <v>39.83947557911845</v>
+        <v>40.00515120355706</v>
       </c>
       <c r="N2" t="n">
-        <v>2758.996880796678</v>
+        <v>2760.881829802117</v>
       </c>
       <c r="O2" t="n">
-        <v>52.52615425477747</v>
+        <v>52.54409414769768</v>
       </c>
       <c r="P2" t="n">
-        <v>431.0446249336604</v>
+        <v>430.3361695195418</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20671,28 +20735,28 @@
         <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2059405842228673</v>
+        <v>-0.2079453818665023</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1341194926578154</v>
+        <v>0.1370043113295404</v>
       </c>
       <c r="M3" t="n">
-        <v>3.014948624138558</v>
+        <v>3.013448563054379</v>
       </c>
       <c r="N3" t="n">
-        <v>14.79366288537522</v>
+        <v>14.77613821124371</v>
       </c>
       <c r="O3" t="n">
-        <v>3.84625309689511</v>
+        <v>3.8439742729685</v>
       </c>
       <c r="P3" t="n">
-        <v>370.122060693208</v>
+        <v>370.1442475354973</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20753,28 +20817,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2588224995421073</v>
+        <v>0.2559857557092233</v>
       </c>
       <c r="J4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2046970778703325</v>
+        <v>0.2016158404376319</v>
       </c>
       <c r="M4" t="n">
-        <v>2.892747707252046</v>
+        <v>2.897119215164144</v>
       </c>
       <c r="N4" t="n">
-        <v>14.06211888365364</v>
+        <v>14.07689442947246</v>
       </c>
       <c r="O4" t="n">
-        <v>3.749949184142852</v>
+        <v>3.751918766374408</v>
       </c>
       <c r="P4" t="n">
-        <v>362.5463486776935</v>
+        <v>362.5777425633732</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20835,28 +20899,28 @@
         <v>0.0935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1916454170066131</v>
+        <v>0.191460489016448</v>
       </c>
       <c r="J5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2309153738339556</v>
+        <v>0.2318576933857963</v>
       </c>
       <c r="M5" t="n">
-        <v>1.979009463119163</v>
+        <v>1.973715635497534</v>
       </c>
       <c r="N5" t="n">
-        <v>6.609124511977506</v>
+        <v>6.588195753982696</v>
       </c>
       <c r="O5" t="n">
-        <v>2.570821758111112</v>
+        <v>2.5667480893112</v>
       </c>
       <c r="P5" t="n">
-        <v>370.8333702040843</v>
+        <v>370.8354167787926</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20917,28 +20981,28 @@
         <v>0.0818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1043393925174011</v>
+        <v>0.1044863631075035</v>
       </c>
       <c r="J6" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K6" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06152022406041868</v>
+        <v>0.06210391156569917</v>
       </c>
       <c r="M6" t="n">
-        <v>2.042411234779506</v>
+        <v>2.036564329583727</v>
       </c>
       <c r="N6" t="n">
-        <v>8.97282904176828</v>
+        <v>8.944230616272522</v>
       </c>
       <c r="O6" t="n">
-        <v>2.995468083917483</v>
+        <v>2.990690658739637</v>
       </c>
       <c r="P6" t="n">
-        <v>393.0015234038981</v>
+        <v>392.9998968989418</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -20999,28 +21063,28 @@
         <v>0.1274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09489457664941743</v>
+        <v>0.09512094543784119</v>
       </c>
       <c r="J7" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K7" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05687424525652796</v>
+        <v>0.05752058430825324</v>
       </c>
       <c r="M7" t="n">
-        <v>2.114544292218582</v>
+        <v>2.108827431781284</v>
       </c>
       <c r="N7" t="n">
-        <v>8.067937393700969</v>
+        <v>8.042459713179893</v>
       </c>
       <c r="O7" t="n">
-        <v>2.840411483165946</v>
+        <v>2.835923079559792</v>
       </c>
       <c r="P7" t="n">
-        <v>394.3468851040263</v>
+        <v>394.3443799092382</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21081,28 +21145,28 @@
         <v>0.1062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.323409601969856</v>
+        <v>0.3228010307710819</v>
       </c>
       <c r="J8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2734486055257762</v>
+        <v>0.2741080837687155</v>
       </c>
       <c r="M8" t="n">
-        <v>2.495844501838541</v>
+        <v>2.491486793909607</v>
       </c>
       <c r="N8" t="n">
-        <v>15.01489236949229</v>
+        <v>14.96952207552496</v>
       </c>
       <c r="O8" t="n">
-        <v>3.87490546587814</v>
+        <v>3.869046662360763</v>
       </c>
       <c r="P8" t="n">
-        <v>392.2590848005063</v>
+        <v>392.2658197810924</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21163,28 +21227,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2366939122913186</v>
+        <v>0.2350616366972197</v>
       </c>
       <c r="J9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1584801145038826</v>
+        <v>0.1574415624784709</v>
       </c>
       <c r="M9" t="n">
-        <v>2.936801448297893</v>
+        <v>2.937268437371281</v>
       </c>
       <c r="N9" t="n">
-        <v>16.07272665909339</v>
+        <v>16.04102609789719</v>
       </c>
       <c r="O9" t="n">
-        <v>4.009080525393995</v>
+        <v>4.005124979060852</v>
       </c>
       <c r="P9" t="n">
-        <v>399.5837426385914</v>
+        <v>399.601806826413</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21245,28 +21309,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1570123720305674</v>
+        <v>0.1581611633353748</v>
       </c>
       <c r="J10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08390966217077245</v>
+        <v>0.08555144682759019</v>
       </c>
       <c r="M10" t="n">
-        <v>2.875490350084157</v>
+        <v>2.87089164589726</v>
       </c>
       <c r="N10" t="n">
-        <v>14.54185652097421</v>
+        <v>14.50506278174657</v>
       </c>
       <c r="O10" t="n">
-        <v>3.813378622819168</v>
+        <v>3.80855127072573</v>
       </c>
       <c r="P10" t="n">
-        <v>403.6791505606101</v>
+        <v>403.6664370323476</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -21327,28 +21391,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01597115276854776</v>
+        <v>0.01680126814583019</v>
       </c>
       <c r="J11" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K11" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001033972302606601</v>
+        <v>0.001152014497982523</v>
       </c>
       <c r="M11" t="n">
-        <v>2.677892947181046</v>
+        <v>2.673170842742571</v>
       </c>
       <c r="N11" t="n">
-        <v>13.3149677109573</v>
+        <v>13.27741630970094</v>
       </c>
       <c r="O11" t="n">
-        <v>3.648968033699021</v>
+        <v>3.643818918346649</v>
       </c>
       <c r="P11" t="n">
-        <v>401.7132002650209</v>
+        <v>401.7040134829953</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -21409,28 +21473,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1126529454308731</v>
+        <v>-0.1109449556406733</v>
       </c>
       <c r="J12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05820059849735626</v>
+        <v>0.05683206185431455</v>
       </c>
       <c r="M12" t="n">
-        <v>2.438773833842977</v>
+        <v>2.438031934433694</v>
       </c>
       <c r="N12" t="n">
-        <v>11.09537124414209</v>
+        <v>11.08150460473233</v>
       </c>
       <c r="O12" t="n">
-        <v>3.33097151656121</v>
+        <v>3.328889395088447</v>
       </c>
       <c r="P12" t="n">
-        <v>401.6133981207527</v>
+        <v>401.5944960134865</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -21491,28 +21555,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1931967202689224</v>
+        <v>-0.1910018689948204</v>
       </c>
       <c r="J13" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K13" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1726400560190399</v>
+        <v>0.1699013414621333</v>
       </c>
       <c r="M13" t="n">
-        <v>2.227393026672348</v>
+        <v>2.229116056302082</v>
       </c>
       <c r="N13" t="n">
-        <v>9.664473459876751</v>
+        <v>9.669324404463833</v>
       </c>
       <c r="O13" t="n">
-        <v>3.108773626347977</v>
+        <v>3.109553730756848</v>
       </c>
       <c r="P13" t="n">
-        <v>400.1008241665464</v>
+        <v>400.0765340247351</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -21573,28 +21637,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2326958052003788</v>
+        <v>-0.2274263082090665</v>
       </c>
       <c r="J14" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K14" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1692830908255958</v>
+        <v>0.1619774490897389</v>
       </c>
       <c r="M14" t="n">
-        <v>3.039137731978521</v>
+        <v>3.057503856427917</v>
       </c>
       <c r="N14" t="n">
-        <v>14.35629438858721</v>
+        <v>14.51678839689232</v>
       </c>
       <c r="O14" t="n">
-        <v>3.788970096027047</v>
+        <v>3.810090339728484</v>
       </c>
       <c r="P14" t="n">
-        <v>401.9602965130352</v>
+        <v>401.9019796554406</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -21655,28 +21719,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2306152251881365</v>
+        <v>-0.2276466421864472</v>
       </c>
       <c r="J15" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K15" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2538976324422196</v>
+        <v>0.2489290473900669</v>
       </c>
       <c r="M15" t="n">
-        <v>2.093507430458319</v>
+        <v>2.102521257100936</v>
       </c>
       <c r="N15" t="n">
-        <v>8.443869154263254</v>
+        <v>8.482343967375268</v>
       </c>
       <c r="O15" t="n">
-        <v>2.905833641876846</v>
+        <v>2.912446388755554</v>
       </c>
       <c r="P15" t="n">
-        <v>401.3073820282419</v>
+        <v>401.2745290951341</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -21718,7 +21782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P312"/>
+  <dimension ref="A1:P313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47131,7 +47195,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>-35.27282663849006,174.08079777972014</t>
+          <t>-35.272774256429564,174.0810121960133</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -47200,6 +47264,88 @@
         </is>
       </c>
       <c r="P312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-35.272643235282345,174.08154849890735</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-35.27368224483601,174.08041701770762</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-35.274391376251906,174.08063815429352</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-35.27505899410528,174.0810016191394</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-35.275606133437954,174.0815274224995</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-35.27607193410178,174.0821039447309</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-35.276511577430796,174.08278259988722</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-35.27690517847072,174.08349355164108</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-35.27720435742357,174.08425179893933</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-35.27752455378625,174.08500842687684</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-35.27778140539651,174.08582613313283</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-35.27801606145219,174.08665681067598</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-35.278137650068444,174.08752394631824</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-35.27832038953089,174.08838699890097</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
